--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyasholiammapkkam_13.408935_80.151242.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Periyasholiammapkkam_13.408935_80.151242.xlsx
@@ -1154,6 +1154,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1161,6 +1166,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1168,6 +1178,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1175,6 +1190,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1182,6 +1202,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6A, 6B, 7A1, 7A2, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1189,6 +1214,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1196,6 +1226,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1203,6 +1238,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1210,6 +1250,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2, 2B3, 2B4, 2B5, 2B6, 2C1, 2C2, 2C3, 2C4A, 2C4B</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1217,6 +1262,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1224,6 +1274,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1231,6 +1286,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1238,6 +1298,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1245,6 +1310,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1252,6 +1322,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1259,6 +1334,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1266,6 +1346,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1273,6 +1358,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1280,6 +1370,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1287,6 +1382,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1294,6 +1394,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1301,6 +1406,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1308,6 +1418,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1315,6 +1430,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2, 3, 4A1A, 4A1B, 4A1C1, 4A1C2, 4A1D, 4A1E1, 4A1E2, 4A2A1, 4A2A2, 4A2B1, 4A2B2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1322,6 +1442,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1329,6 +1454,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B1, 2A1B2, 2A1C, 2A2, 2B, 2C, 2D1, 2D2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1336,6 +1466,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1343,6 +1478,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1350,6 +1490,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 2A, 2B, 3A, 3B1, 3B2</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1357,6 +1502,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1364,6 +1514,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1371,6 +1526,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1378,6 +1538,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1385,6 +1550,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1392,6 +1562,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1A, 1C1B, 1C1C, 1C2, 1C3, 1C4, 1C5, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7, 2A8, 2A9, 2B, 2C1, 2C2, 2C3, 2C4</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1399,6 +1574,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1406,6 +1586,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1413,6 +1598,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1420,6 +1610,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1427,6 +1622,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B2, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1434,6 +1634,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A1A, 4A1B, 4A2, 4A4, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1441,6 +1646,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1448,6 +1658,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1455,6 +1670,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1462,6 +1682,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1469,6 +1694,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1476,6 +1706,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1483,6 +1718,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1490,6 +1730,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1497,6 +1742,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2, 3A1, 3A2, 3B1, 3B2, 3C, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1504,6 +1754,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1511,6 +1766,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1518,6 +1778,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1525,6 +1790,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1532,6 +1802,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1539,6 +1814,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1546,6 +1826,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1553,6 +1838,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1560,6 +1850,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1567,6 +1862,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1574,6 +1874,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1581,6 +1886,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1588,6 +1898,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1595,6 +1910,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1602,6 +1922,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1609,6 +1934,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1616,6 +1946,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1623,6 +1958,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4, 1B1, 1B2, 2B1, 3</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1630,6 +1970,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1637,6 +1982,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 2</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1644,6 +1994,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1651,6 +2006,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1658,6 +2018,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2A, 1A3, 1A4, 1A5, 1A6, 1B, 20, 2A1A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1665,6 +2030,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1672,6 +2042,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 2B, 3A1, 3A2A, 3A3, 3B1, 3B2, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1679,6 +2054,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1686,6 +2066,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1693,6 +2078,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1700,6 +2090,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1707,11 +2102,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>
